--- a/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
+++ b/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F1188B-6872-4B51-B80B-D76318A671AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964CE466-926E-4406-98C6-11B2A609F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-645" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
   <si>
     <t>id</t>
   </si>
@@ -312,12 +312,81 @@
   <si>
     <t>python</t>
   </si>
+  <si>
+    <t>Stell dir vor, du organisierst eine Party mit deinen Freunden und hast mehrere Pizzas bestellt. Um sicherzustellen, dass jeder gleich viele Pizzastücke bekommt, musst du die Gesamtzahl der Pizzastücke durch die Anzahl der Freunde teilen. Deine Aufgabe ist es, eine Funktion teile_pizza zu implementieren, die die Anzahl der Pizzastücke und die Anzahl der Freunde entgegennimmt und die Anzahl der Pizzastücke berechnet, die jeder Freund bekommt. Die Funktion soll die ganzzahlige Anzahl der Pizzastücke pro Person zurückgeben. Wenn es weniger Pizzastücke als Freunde gibt, sollte die Funktion 0 zurückgeben.</t>
+  </si>
+  <si>
+    <t>Pizza teilen</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Stell dir vor, du organisierst eine Party mit deinen Freunden und hast mehrere Pizzas bestellt. Um sicherzustellen, dass jeder gleich viele Pizzastücke bekommt, musst du die Gesamtzahl der Pizzastücke durch die Anzahl der Freunde teilen. Deine Aufgabe ist es, eine Funktion &lt;code&gt;teile_pizza&lt;/code&gt; zu implementieren, die die Anzahl der Pizzastücke und die Anzahl der Freunde entgegennimmt und die Anzahl der Pizzastücke berechnet, die jeder Freund bekommt. Die Funktion soll die ganzzahlige Anzahl der Pizzastücke pro Person zurückgeben. Wenn es weniger Pizzastücke als Freunde gibt, sollte die Funktion 0 zurückgeben.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>import unittest
+class TestTeilePizza(unittest.TestCase):
+    def test_teile_pizza(self):
+        self.assertEqual(teile_pizza(8, 4), 2)
+        self.assertEqual(teile_pizza(10, 0), 0)
+        self.assertEqual(teile_pizza(3, 4), 0)
+if __name__ == "__main__":
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>pizzateilung.py</t>
+  </si>
+  <si>
+    <t>def teile_pizza(pizzastuecke, freunde):
+    # Dein Code hier</t>
+  </si>
+  <si>
+    <t>teile_pizza</t>
+  </si>
+  <si>
+    <t>12, 3</t>
+  </si>
+  <si>
+    <t>Wochenplanung</t>
+  </si>
+  <si>
+    <t>In der Wochenplanung einer Studentenverbindung wird festgelegt, wer an welchem Tag der Woche für das Abendessen zuständig ist. Die Zuweisung der Kochtage erfolgt zyklisch unter den Mitgliedern. Deine Aufgabe besteht darin, eine Funktion assign_cooking_day zu implementieren, die den Namen des für einen bestimmten Tag zuständigen Mitglieds zurückgibt. Die Funktion nimmt zwei Parameter: day_number, die Nummer des Tages, und members, eine Liste der Namen der Mitglieder. Die Zählung beginnt bei Tag 1, der dem ersten Element in der Mitgliederliste entspricht. Nutze den Modulo-Operator, um den entsprechenden Index in der Mitgliederliste zu bestimmen und den Namen des zuständigen Mitglieds zurückzugeben. Dies ist besonders nützlich, um auch für Tage weit in der Zukunft den Koch zuordnen zu können, ohne die Liste manuell erweitern zu müssen.</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;In der Wochenplanung einer Studentenverbindung wird festgelegt, wer an welchem Tag der Woche für das Abendessen zuständig ist. Die Zuweisung der Kochtage erfolgt zyklisch unter den Mitgliedern. Deine Aufgabe besteht darin, eine Funktion &lt;b&gt;assign_cooking_day&lt;/b&gt; zu implementieren, die den Namen des für einen bestimmten Tag zuständigen Mitglieds zurückgibt. Die Funktion nimmt zwei Parameter: &lt;i&gt;day_number&lt;/i&gt;, die Nummer des Tages, und &lt;i&gt;members&lt;/i&gt;, eine Liste der Namen der Mitglieder. Die Zählung beginnt bei Tag 1, der dem ersten Element in der Mitgliederliste entspricht. Nutze den Modulo-Operator, um den entsprechenden Index in der Mitgliederliste zu bestimmen und den Namen des zuständigen Mitglieds zurückzugeben. Dies ist besonders nützlich, um auch für Tage weit in der Zukunft den Koch zuordnen zu können, ohne die Liste manuell erweitern zu müssen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>cooking_assignment.py</t>
+  </si>
+  <si>
+    <t>import unittest
+from cooking_assignment import assign_cooking_day
+class TestCookingAssignment(unittest.TestCase):
+    def test_assign_cooking_day(self):
+        members = ["Alice", "Bob", "Charlie", "Dana"]
+        self.assertEqual(assign_cooking_day(1, members), "Alice")
+        self.assertEqual(assign_cooking_day(5, members), "Alice")
+        self.assertEqual(assign_cooking_day(7, members), "Charlie")
+if __name__ == "__main__":
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>assign_cooking_day</t>
+  </si>
+  <si>
+    <t>10, ["Alice", "Bob", "Charlie", "Dana"]</t>
+  </si>
+  <si>
+    <t>def assign_cooking_day(day_number, members):
+    # Implementiere hier die Funktion
+# Beispielausführung der Funktion
+if __name__ == "__main__":
+    print(assign_cooking_day(10, ["Alice", "Bob", "Charlie", "Dana"]))</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +466,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -432,7 +506,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -493,6 +567,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Gut" xfId="1" builtinId="26"/>
@@ -800,8 +885,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="28.5" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="28.5"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
@@ -819,7 +904,7 @@
     <col min="15" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" s="6" customFormat="1" ht="18.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -861,46 +946,47 @@
       </c>
       <c r="N1" s="13"/>
     </row>
-    <row r="2" spans="1:14" ht="216.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+    <row r="2" spans="1:14" s="6" customFormat="1" ht="285">
+      <c r="A2" s="25">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="26">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="27">
         <v>5</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="27">
         <v>0</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="M2" s="27"/>
+      <c r="N2" s="28"/>
+    </row>
+    <row r="3" spans="1:14" ht="114.75">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -939,7 +1025,7 @@
       </c>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="153">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -980,7 +1066,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="178.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="178.5">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -1021,7 +1107,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="191.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="191.25">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -1060,6 +1146,88 @@
       </c>
       <c r="M6" s="14" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="187.5">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1">
+        <v>14</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="225">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1074,14 +1242,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="129.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="60" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="60" customHeight="1">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -1109,7 +1277,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="60" customHeight="1">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -1123,7 +1291,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="60" customHeight="1">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -1137,7 +1305,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="60" customHeight="1">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -1151,7 +1319,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="60" customHeight="1">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -1165,277 +1333,297 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="60" customHeight="1">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="60" customHeight="1">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="60" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="60" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="60" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="60" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="60" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="60" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="60" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="60" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="60" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="60" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="60" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="60" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="60" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="60" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="60" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="60" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="60" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="60" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="60" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="60" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="60" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="60" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="60" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="60" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="D32" s="4"/>
     </row>
-    <row r="33" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="60" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="60" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="60" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="D35" s="5"/>
     </row>
-    <row r="36" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="60" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="D36" s="5"/>
     </row>
-    <row r="37" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="60" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="D37" s="5"/>
     </row>
-    <row r="38" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="60" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="D38" s="5"/>
     </row>
-    <row r="39" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="60" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="D39" s="5"/>
     </row>
-    <row r="40" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="60" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="D40" s="5"/>
     </row>
-    <row r="41" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="60" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="D41" s="5"/>
     </row>
-    <row r="42" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="60" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="D42" s="5"/>
     </row>
-    <row r="43" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="60" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="D43" s="5"/>
     </row>
-    <row r="44" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="60" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="D44" s="5"/>
     </row>
-    <row r="45" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="60" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="D45" s="5"/>
     </row>
-    <row r="46" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="60" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="D46" s="5"/>
     </row>
-    <row r="47" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="60" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="D47" s="5"/>
     </row>
-    <row r="48" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="60" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="D48" s="5"/>
     </row>
-    <row r="49" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="60" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="D49" s="5"/>
     </row>
-    <row r="50" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="60" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="D50" s="5"/>
     </row>
-    <row r="51" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="60" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="D51" s="5"/>
     </row>
-    <row r="52" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="60" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="D52" s="5"/>
     </row>
-    <row r="53" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="60" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="D53" s="5"/>
     </row>
-    <row r="54" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="60" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="D54" s="5"/>
     </row>
-    <row r="55" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="60" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="60" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="60" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
     </row>
-    <row r="58" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="60" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="60" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="D59" s="5"/>
     </row>
-    <row r="60" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="60" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="D60" s="5"/>
     </row>
-    <row r="61" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="60" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
     </row>
-    <row r="62" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="60" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="D62" s="5"/>

--- a/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
+++ b/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964CE466-926E-4406-98C6-11B2A609F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57907BD-E52C-4A67-AACA-409FF9A4922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-645" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,15 +96,6 @@
     <t>Erweitere das vorhandene Python-Programm so, dass die Funktion wilkommen() statt „Hallo“ nun „Hallo Welt“ ausgibt.</t>
   </si>
   <si>
-    <t>import unittest
-class TestWillkommen(unittest.TestCase):
-    def test_willkommen(self):
-        self.assertEqual(willkommen(), "Hallo Welt")
-# Dies führt die Tests aus, wenn das Skript direkt ausgeführt wird.
-if __name__ == '__main__':
-    unittest.main()</t>
-  </si>
-  <si>
     <t xml:space="preserve">    &lt;h1&gt;Eure erste Aufgabe:&lt;/h1&gt;
     &lt;p&gt;Erweitere das vorhandene Python-Programm so, dass die Funktion wilkommen() statt „Hallo“ nun „Hallo Welt“ ausgibt.&lt;/p&gt;
     &lt;h2&gt;Hinweise zu Programmieraufgaben:&lt;/h2&gt;
@@ -125,56 +116,6 @@
     <t>Python Variabeln</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>initialisiere_variable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> zu implementieren, die eine Variable namens </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>meine_variable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.</t>
-    </r>
-  </si>
-  <si>
-    <t>import unittest
-class TestVariablenEinfuehrung(unittest.TestCase):
-    def test_variable_initialisierung(self):
-        self.assertEqual(initialisiere_variable(), 100, "Die Variable sollte mit 100 initialisiert werden.")
-# Code zum Ausführen der Tests
-if __name__ == "__main__":
-    unittest.main()</t>
-  </si>
-  <si>
     <t>&lt;p&gt;In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens &lt;code&gt;initialisiere_variable&lt;/code&gt; zu implementieren, die eine Variable namens &lt;code&gt;meine_variable&lt;/code&gt; deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.&lt;/p&gt;</t>
   </si>
   <si>
@@ -187,23 +128,6 @@
     <t>Python Anweisungen</t>
   </si>
   <si>
-    <t>In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen variable_assignments, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt. Achte darauf, die Zuweisungsoperatoren korrekt zu verwenden und nicht in den Fehler zu verfallen, der im Bild dargestellt ist.</t>
-  </si>
-  <si>
-    <t>import unittest
-class TestVariableAssignments(unittest.TestCase):
-    def test_results(self):
-        self.assertEqual(variable_assignments(5, 3), (8, 2, 15))
-        self.assertEqual(variable_assignments(-2, 4), (2, -6, -8))
-        self.assertEqual(variable_assignments(0, 0), (0, 0, 0))
-# Dieser Block ist nur notwendig, wenn du die Tests ausführst.
-if __name__ == '__main__':
-    unittest.main()</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen &lt;code&gt;variable_assignments&lt;/code&gt;, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt. Achte darauf, die Zuweisungsoperatoren korrekt zu verwenden und nicht in den Fehler zu verfallen, der im Bild dargestellt ist.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>variable_assignments.py</t>
   </si>
   <si>
@@ -217,18 +141,6 @@
   </si>
   <si>
     <t>In dieser Aufgabe sollst du eine Funktion namens verarbeite_optionale_daten implementieren, die einen Parameter daten entgegennimmt. Dieser Parameter könnte einen beliebigen Wert oder None enthalten. Deine Aufgabe ist es, die Funktion so zu gestalten, dass sie überprüft, ob daten None ist oder nicht. Falls daten None ist, soll die Funktion den String "Keine Daten vorhanden." zurückgeben. Andernfalls soll die Funktion den String "Daten verarbeitet: [DATEN]" zurückgeben, wobei [DATEN] der Wert des Parameters daten ist.</t>
-  </si>
-  <si>
-    <t>import unittest
-class TestVerarbeiteOptionaleDaten(unittest.TestCase):
-    def test_mit_none(self):
-        self.assertEqual(verarbeite_optionale_daten(None), "Keine Daten vorhanden.")
-    def test_mit_daten(self):
-        self.assertEqual(verarbeite_optionale_daten("Ein Teststring"), "Daten verarbeitet: Ein Teststring")
-    def test_mit_leerem_string(self):
-        self.assertEqual(verarbeite_optionale_daten(""), "Daten verarbeitet: ")
-if __name__ == "__main__":
-    unittest.main()</t>
   </si>
   <si>
     <t>&lt;p&gt;In dieser Aufgabe sollst du eine Funktion namens &lt;code&gt;verarbeite_optionale_daten&lt;/code&gt; implementieren, die einen Parameter &lt;code&gt;daten&lt;/code&gt; entgegennimmt. Dieser Parameter könnte einen beliebigen Wert oder &lt;code&gt;None&lt;/code&gt; enthalten. Deine Aufgabe ist es, die Funktion so zu gestalten, dass sie überprüft, ob &lt;code&gt;daten&lt;/code&gt; &lt;code&gt;None&lt;/code&gt; ist oder nicht. Falls &lt;code&gt;daten&lt;/code&gt; &lt;code&gt;None&lt;/code&gt; ist, soll die Funktion den String "Keine Daten vorhanden." zurückgeben. Andernfalls soll die Funktion den String "Daten verarbeitet: [DATEN]" zurückgeben, wobei [DATEN] der Wert des Parameters &lt;code&gt;daten&lt;/code&gt; ist.&lt;/p&gt;</t>
@@ -248,18 +160,6 @@
   <si>
     <t>In dieser Aufgabe wirst du eine Funktion namens convert_to_number erstellen, die einen String als Eingabeparameter annimmt und versucht, diesen in eine Zahl umzuwandeln. Deine Aufgabe ist es, eine Funktion zu implementieren, die diesen String prüft und in eine ganze Zahl oder eine Fließkommazahl umwandelt, je nachdem, ob der String eine Ganzzahl oder eine Fließkommazahl darstellt.
 Falls der String nicht in eine Zahl umgewandelt werden kann, sollte deine Funktion None zurückgeben. Es ist wichtig, Fehlerbehandlung zu implementieren, um sicherzustellen, dass deine Funktion robust und sicher gegenüber ungültigen Eingaben ist.</t>
-  </si>
-  <si>
-    <t>import unittest
-class TestConvertToNumber(unittest.TestCase):
-    def test_integer_conversion(self):
-        self.assertEqual(convert_to_number("123"), 123)
-    def test_float_conversion(self):
-        self.assertEqual(convert_to_number("45.67"), 45.67)
-    def test_invalid_conversion(self):
-        self.assertIsNone(convert_to_number("abc"))
-if __name__ == '__main__':
-    unittest.main()</t>
   </si>
   <si>
     <t>&lt;p&gt;In dieser Aufgabe wirst du eine Funktion namens &lt;code&gt;convert_to_number&lt;/code&gt; erstellen, die einen String als Eingabeparameter annimmt und versucht, diesen in eine Zahl umzuwandeln. Deine Aufgabe ist es, eine Funktion zu implementieren, die diesen String prüft und in eine ganze Zahl oder eine Fließkommazahl umwandelt, je nachdem, ob der String eine Ganzzahl oder eine Fließkommazahl darstellt.&lt;/p&gt;
@@ -320,16 +220,6 @@
   </si>
   <si>
     <t>&lt;p&gt;Stell dir vor, du organisierst eine Party mit deinen Freunden und hast mehrere Pizzas bestellt. Um sicherzustellen, dass jeder gleich viele Pizzastücke bekommt, musst du die Gesamtzahl der Pizzastücke durch die Anzahl der Freunde teilen. Deine Aufgabe ist es, eine Funktion &lt;code&gt;teile_pizza&lt;/code&gt; zu implementieren, die die Anzahl der Pizzastücke und die Anzahl der Freunde entgegennimmt und die Anzahl der Pizzastücke berechnet, die jeder Freund bekommt. Die Funktion soll die ganzzahlige Anzahl der Pizzastücke pro Person zurückgeben. Wenn es weniger Pizzastücke als Freunde gibt, sollte die Funktion 0 zurückgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>import unittest
-class TestTeilePizza(unittest.TestCase):
-    def test_teile_pizza(self):
-        self.assertEqual(teile_pizza(8, 4), 2)
-        self.assertEqual(teile_pizza(10, 0), 0)
-        self.assertEqual(teile_pizza(3, 4), 0)
-if __name__ == "__main__":
-    unittest.main()</t>
   </si>
   <si>
     <t>pizzateilung.py</t>
@@ -380,6 +270,84 @@
 # Beispielausführung der Funktion
 if __name__ == "__main__":
     print(assign_cooking_day(10, ["Alice", "Bob", "Charlie", "Dana"]))</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen &lt;code&gt;variable_assignments&lt;/code&gt;, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen variable_assignments, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt.</t>
+  </si>
+  <si>
+    <t>In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens initialisiere_variable zu implementieren, die eine Variable namens meine_variable deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.</t>
+  </si>
+  <si>
+    <t>import unittest
+from halloWelt import willkommen
+class TestWillkommen(unittest.TestCase):
+    def test_willkommen(self):
+        self.assertEqual(willkommen(), "Hallo Welt")
+# Dies führt die Tests aus, wenn das Skript direkt ausgeführt wird.
+if __name__ == '__main__':
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>import unittest
+from variablen_einfuehrung import initialisiere_variable
+class TestVariablenEinfuehrung(unittest.TestCase):
+    def test_variable_initialisierung(self):
+        self.assertEqual(initialisiere_variable(), 100, "Die Variable sollte mit 100 initialisiert werden.")
+# Code zum Ausführen der Tests
+if __name__ == "__main__":
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>import unittest
+from variable_assignments import variable_assignments
+class TestVariableAssignments(unittest.TestCase):
+    def test_results(self):
+        self.assertEqual(variable_assignments(5, 3), (8, 2, 15))
+        self.assertEqual(variable_assignments(-2, 4), (2, -6, -8))
+        self.assertEqual(variable_assignments(0, 0), (0, 0, 0))
+# Dieser Block ist nur notwendig, wenn du die Tests ausführst.
+if __name__ == '__main__':
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>import unittest
+from datentyp_none import verarbeite_optionale_daten
+class TestVerarbeiteOptionaleDaten(unittest.TestCase):
+    def test_mit_none(self):
+        self.assertEqual(verarbeite_optionale_daten(None), "Keine Daten vorhanden.")
+    def test_mit_daten(self):
+        self.assertEqual(verarbeite_optionale_daten("Ein Teststring"), "Daten verarbeitet: Ein Teststring")
+    def test_mit_leerem_string(self):
+        self.assertEqual(verarbeite_optionale_daten(""), "Daten verarbeitet: ")
+if __name__ == "__main__":
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>import unittest
+from string_to_number_converter import convert_to_number
+class TestConvertToNumber(unittest.TestCase):
+    def test_integer_conversion(self):
+        self.assertEqual(convert_to_number("123"), 123)
+    def test_float_conversion(self):
+        self.assertEqual(convert_to_number("45.67"), 45.67)
+    def test_invalid_conversion(self):
+        self.assertIsNone(convert_to_number("abc"))
+if __name__ == '__main__':
+    unittest.main()</t>
+  </si>
+  <si>
+    <t>import unittest
+from pizzateilung import teile_pizza
+class TestTeilePizza(unittest.TestCase):
+    def test_teile_pizza(self):
+        self.assertEqual(teile_pizza(8, 4), 2)
+        self.assertEqual(teile_pizza(10, 0), 0)
+        self.assertEqual(teile_pizza(3, 4), 0)
+if __name__ == "__main__":
+    unittest.main()</t>
   </si>
 </sst>
 </file>
@@ -506,7 +474,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -544,19 +512,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -578,6 +537,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Gut" xfId="1" builtinId="26"/>
@@ -947,288 +912,292 @@
       <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:14" s="6" customFormat="1" ht="285">
-      <c r="A2" s="25">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="23">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="24">
+        <v>5</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="24">
+        <v>0</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25"/>
+    </row>
+    <row r="3" spans="1:14" s="25" customFormat="1" ht="150">
+      <c r="A3" s="25">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25">
+        <v>1</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="25">
+        <v>6</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="25">
+        <v>0</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="6" customFormat="1" ht="195">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23">
+        <v>1</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="24">
+        <v>7</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="25"/>
+    </row>
+    <row r="5" spans="1:14" s="6" customFormat="1" ht="225">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23">
+        <v>1</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="24">
+        <v>17</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="25"/>
+    </row>
+    <row r="6" spans="1:14" s="6" customFormat="1" ht="240">
+      <c r="A6" s="22">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23">
+        <v>1</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="24">
+        <v>15</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="25"/>
+    </row>
+    <row r="7" spans="1:14" s="6" customFormat="1" ht="165">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="8">
+        <v>14</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="25"/>
+    </row>
+    <row r="8" spans="1:14" s="6" customFormat="1" ht="195">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="8">
+        <v>14</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="27">
-        <v>5</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="27">
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="8">
         <v>0</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="28"/>
-    </row>
-    <row r="3" spans="1:14" ht="114.75">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="14">
-        <v>6</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="14">
-        <v>0</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="153">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="14">
-        <v>7</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="14">
-        <v>0</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="178.5">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16">
-        <v>1</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="14">
-        <v>8</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="14">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="191.25">
-      <c r="A6" s="15">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="14">
-        <v>15</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="14">
-        <v>0</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="187.5">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="1">
-        <v>14</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="14" t="s">
+      <c r="L8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="225">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="1">
-        <v>14</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>71</v>
-      </c>
+      <c r="M8" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1264,73 +1233,73 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="60" customHeight="1">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>55</v>
+      <c r="C2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" customHeight="1">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>2</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="60" customHeight="1">
+      <c r="A4" s="14">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14">
+        <v>3</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="60" customHeight="1">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15">
-        <v>3</v>
-      </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60" customHeight="1">
+      <c r="A5" s="14">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14">
+        <v>4</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="60" customHeight="1">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15">
-        <v>4</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>53</v>
+      <c r="D5" s="20" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="60" customHeight="1">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>5</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>54</v>
+      <c r="C6" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" customHeight="1">
@@ -1340,11 +1309,11 @@
       <c r="B7" s="3">
         <v>6</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>61</v>
+      <c r="C7" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60" customHeight="1">
@@ -1355,10 +1324,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" customHeight="1">

--- a/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
+++ b/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57907BD-E52C-4A67-AACA-409FF9A4922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E154C4-3E70-42C4-89D7-B90042A776DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-645" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -91,26 +91,6 @@
   </si>
   <si>
     <t>Hallo Welt</t>
-  </si>
-  <si>
-    <t>Erweitere das vorhandene Python-Programm so, dass die Funktion wilkommen() statt „Hallo“ nun „Hallo Welt“ ausgibt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    &lt;h1&gt;Eure erste Aufgabe:&lt;/h1&gt;
-    &lt;p&gt;Erweitere das vorhandene Python-Programm so, dass die Funktion wilkommen() statt „Hallo“ nun „Hallo Welt“ ausgibt.&lt;/p&gt;
-    &lt;h2&gt;Hinweise zu Programmieraufgaben:&lt;/h2&gt;
-    &lt;h3&gt;Ausführen und Testen:&lt;/h3&gt;
-    &lt;p&gt;Keine Sorge, ihr müsst nicht selbst überprüfen, ob euer Code korrekt funktioniert. Unser System übernimmt das automatisch für euch. Wenn alles passt, seht ihr eine Punktzahl von 100/100. Das ist euer Ziel!&lt;/p&gt;
-    &lt;h3&gt;Feedback:&lt;/h3&gt;
-    &lt;p&gt;Falls ihr mal nicht weiterwisst, steht euch unser Tutor Kai mit Rat und Tat zur Seite. Nachdem ihr euren Code zum ersten Mal ausgeführt habt, werdet ihr zwei Feedback-Buttons sehen, die euch helfen können. Da wir das Feedback-System noch verbessern möchten, würden wir uns freuen, wenn ihr nach der Nutzung eine Bewertung zwischen 1 und 7 Sternen abgebt. Ihr könnt auch gerne zusätzliche Kommentare hinterlassen, falls ihr spezielle Anregungen oder Wünsche habt.&lt;/p&gt;
-    &lt;p&gt;Wir wünschen euch viel Erfolg und Spaß bei dieser ersten Herausforderung!&lt;/p&gt;
-    &lt;p&gt;Euer &lt;strong&gt;GOALS -Team&lt;/strong&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>halloWelt.py</t>
-  </si>
-  <si>
-    <t>willkommen</t>
   </si>
   <si>
     <t>Python Variabeln</t>
@@ -203,11 +183,6 @@
   <si>
     <t>def convert_to_number(s):
     # Implementiere die Funktion hier</t>
-  </si>
-  <si>
-    <t>def willkommen():
-    return "Hallo" # Passen Sie diese Zeile an.
-print(willkommen())</t>
   </si>
   <si>
     <t>python</t>
@@ -279,16 +254,6 @@
   </si>
   <si>
     <t>In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens initialisiere_variable zu implementieren, die eine Variable namens meine_variable deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.</t>
-  </si>
-  <si>
-    <t>import unittest
-from halloWelt import willkommen
-class TestWillkommen(unittest.TestCase):
-    def test_willkommen(self):
-        self.assertEqual(willkommen(), "Hallo Welt")
-# Dies führt die Tests aus, wenn das Skript direkt ausgeführt wird.
-if __name__ == '__main__':
-    unittest.main()</t>
   </si>
   <si>
     <t>import unittest
@@ -348,6 +313,83 @@
         self.assertEqual(teile_pizza(3, 4), 0)
 if __name__ == "__main__":
     unittest.main()</t>
+  </si>
+  <si>
+    <t>CPP TEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;h1&gt;CPP Test&lt;/h1&gt;
+</t>
+  </si>
+  <si>
+    <t>main.cpp</t>
+  </si>
+  <si>
+    <t>testFile</t>
+  </si>
+  <si>
+    <t>#define DOCTEST_CONFIG_IMPLEMENT_WITH_MAIN
+#include &lt;JsonReporter.h&gt;
+#include "Calculator.h"
+#include "Greeter.h"
+TEST_CASE("Calculator add method") {
+    Calculator calc;
+    SUBCASE("Adding positive numbers") {
+        REQUIRE(calc.add(5, 3) == 8);
+    }
+    SUBCASE("Adding negative numbers") {
+        REQUIRE(calc.add(-2, -4) == -6);
+    }
+}
+TEST_CASE("Greeter greet method") {
+    Greeter greeter;
+    SUBCASE("Greeting a person") {
+        REQUIRE(greeter.greet("John") == "Hello, John!");
+    }
+    SUBCASE("Greeting an empty string") {
+        REQUIRE(greeter.greet("") == "Hello, !");
+    }
+}</t>
+  </si>
+  <si>
+    <t>#include &lt;iostream&gt;
+#include "Calculator.h"
+#include "Greeter.h"
+int main() {
+    Calculator calc;
+    Greeter greeter;
+    int sum = calc.add(5, 3);
+    std::cout &lt;&lt; "Sum of 5 and 3 is: " &lt;&lt; sum &lt;&lt; std::endl;
+    std::string greeting = greeter.greet("World");
+    std::cout &lt;&lt; greeting &lt;&lt; std::endl;
+    return 0;
+}</t>
+  </si>
+  <si>
+    <t>Calculator.h</t>
+  </si>
+  <si>
+    <t>class Calculator {
+public:
+    int add(int a, int b) {
+        return a + b;
+    }
+};</t>
+  </si>
+  <si>
+    <t>Greeter.h</t>
+  </si>
+  <si>
+    <t>#include &lt;string&gt;
+class Greeter {
+public:
+    std::string greet(const std::string&amp; name) {
+        return "Hello, " + name + "!";
+    }
+};</t>
+  </si>
+  <si>
+    <t>cpp</t>
   </si>
 </sst>
 </file>
@@ -911,7 +953,7 @@
       </c>
       <c r="N1" s="13"/>
     </row>
-    <row r="2" spans="1:14" s="6" customFormat="1" ht="285">
+    <row r="2" spans="1:14" s="6" customFormat="1" ht="409.5">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -919,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D2" s="24">
         <v>5</v>
@@ -928,26 +970,24 @@
         <v>18</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J2" s="24">
         <v>0</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>22</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="L2" s="24"/>
       <c r="M2" s="24"/>
       <c r="N2" s="25"/>
     </row>
@@ -959,25 +999,25 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D3" s="25">
         <v>6</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J3" s="25">
         <v>0</v>
@@ -986,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="6" customFormat="1" ht="195">
@@ -997,25 +1037,25 @@
         <v>1</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" s="24">
         <v>7</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J4" s="24">
         <v>0</v>
@@ -1024,10 +1064,10 @@
         <v>16</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N4" s="25"/>
     </row>
@@ -1039,25 +1079,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" s="24">
         <v>17</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J5" s="24">
         <v>0</v>
@@ -1066,10 +1106,10 @@
         <v>16</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M5" s="24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N5" s="25"/>
     </row>
@@ -1081,25 +1121,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D6" s="24">
         <v>15</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J6" s="24">
         <v>0</v>
@@ -1108,10 +1148,10 @@
         <v>16</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N6" s="25"/>
     </row>
@@ -1123,25 +1163,25 @@
         <v>1</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D7" s="8">
         <v>14</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -1150,10 +1190,10 @@
         <v>16</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N7" s="25"/>
     </row>
@@ -1165,25 +1205,25 @@
         <v>1</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8">
         <v>14</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
@@ -1192,10 +1232,10 @@
         <v>16</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N8" s="25"/>
     </row>
@@ -1240,10 +1280,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" customHeight="1">
@@ -1254,10 +1294,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="60" customHeight="1">
@@ -1268,10 +1308,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" customHeight="1">
@@ -1282,10 +1322,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="60" customHeight="1">
@@ -1296,10 +1336,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" customHeight="1">
@@ -1310,10 +1350,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60" customHeight="1">
@@ -1324,21 +1364,39 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="60" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="60" customHeight="1">
       <c r="A11" s="3"/>

--- a/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
+++ b/files/programming-tasks/programmieraufgaben_basicTasks_genByGPT_sven.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E154C4-3E70-42C4-89D7-B90042A776DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944602FA-AF9E-4BE9-B3F8-FC3C9396AE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="25875" windowHeight="20805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -90,15 +90,9 @@
     <t>testClassName</t>
   </si>
   <si>
-    <t>Hallo Welt</t>
-  </si>
-  <si>
     <t>Python Variabeln</t>
   </si>
   <si>
-    <t>&lt;p&gt;In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens &lt;code&gt;initialisiere_variable&lt;/code&gt; zu implementieren, die eine Variable namens &lt;code&gt;meine_variable&lt;/code&gt; deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>variablen_einfuehrung.py</t>
   </si>
   <si>
@@ -121,9 +115,6 @@
   </si>
   <si>
     <t>In dieser Aufgabe sollst du eine Funktion namens verarbeite_optionale_daten implementieren, die einen Parameter daten entgegennimmt. Dieser Parameter könnte einen beliebigen Wert oder None enthalten. Deine Aufgabe ist es, die Funktion so zu gestalten, dass sie überprüft, ob daten None ist oder nicht. Falls daten None ist, soll die Funktion den String "Keine Daten vorhanden." zurückgeben. Andernfalls soll die Funktion den String "Daten verarbeitet: [DATEN]" zurückgeben, wobei [DATEN] der Wert des Parameters daten ist.</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;In dieser Aufgabe sollst du eine Funktion namens &lt;code&gt;verarbeite_optionale_daten&lt;/code&gt; implementieren, die einen Parameter &lt;code&gt;daten&lt;/code&gt; entgegennimmt. Dieser Parameter könnte einen beliebigen Wert oder &lt;code&gt;None&lt;/code&gt; enthalten. Deine Aufgabe ist es, die Funktion so zu gestalten, dass sie überprüft, ob &lt;code&gt;daten&lt;/code&gt; &lt;code&gt;None&lt;/code&gt; ist oder nicht. Falls &lt;code&gt;daten&lt;/code&gt; &lt;code&gt;None&lt;/code&gt; ist, soll die Funktion den String "Keine Daten vorhanden." zurückgeben. Andernfalls soll die Funktion den String "Daten verarbeitet: [DATEN]" zurückgeben, wobei [DATEN] der Wert des Parameters &lt;code&gt;daten&lt;/code&gt; ist.&lt;/p&gt;</t>
   </si>
   <si>
     <t>datentyp_none.py</t>
@@ -140,16 +131,6 @@
   <si>
     <t>In dieser Aufgabe wirst du eine Funktion namens convert_to_number erstellen, die einen String als Eingabeparameter annimmt und versucht, diesen in eine Zahl umzuwandeln. Deine Aufgabe ist es, eine Funktion zu implementieren, die diesen String prüft und in eine ganze Zahl oder eine Fließkommazahl umwandelt, je nachdem, ob der String eine Ganzzahl oder eine Fließkommazahl darstellt.
 Falls der String nicht in eine Zahl umgewandelt werden kann, sollte deine Funktion None zurückgeben. Es ist wichtig, Fehlerbehandlung zu implementieren, um sicherzustellen, dass deine Funktion robust und sicher gegenüber ungültigen Eingaben ist.</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;In dieser Aufgabe wirst du eine Funktion namens &lt;code&gt;convert_to_number&lt;/code&gt; erstellen, die einen String als Eingabeparameter annimmt und versucht, diesen in eine Zahl umzuwandeln. Deine Aufgabe ist es, eine Funktion zu implementieren, die diesen String prüft und in eine ganze Zahl oder eine Fließkommazahl umwandelt, je nachdem, ob der String eine Ganzzahl oder eine Fließkommazahl darstellt.&lt;/p&gt;
-&lt;p&gt;Falls der String nicht in eine Zahl umgewandelt werden kann, sollte deine Funktion &lt;code&gt;None&lt;/code&gt; zurückgeben. Es ist wichtig, Fehlerbehandlung zu implementieren, um sicherzustellen, dass deine Funktion robust und sicher gegenüber ungültigen Eingaben ist.&lt;/p&gt;
-&lt;p&gt;Beispiel:&lt;/p&gt;
-&lt;ul&gt;
-&lt;p&gt;- Eingabe: "123" -&gt; Ausgabe: 123&lt;/p&gt;
-&lt;p&gt;- Eingabe: "45.67" -&gt; Ausgabe: 45.67&lt;/p&gt;
-&lt;p&gt;- Eingabe: "abc" -&gt; Ausgabe: None&lt;/p&gt;
-&lt;/ul&gt;</t>
   </si>
   <si>
     <t>string_to_number_converter.py</t>
@@ -194,9 +175,6 @@
     <t>Pizza teilen</t>
   </si>
   <si>
-    <t>&lt;p&gt;Stell dir vor, du organisierst eine Party mit deinen Freunden und hast mehrere Pizzas bestellt. Um sicherzustellen, dass jeder gleich viele Pizzastücke bekommt, musst du die Gesamtzahl der Pizzastücke durch die Anzahl der Freunde teilen. Deine Aufgabe ist es, eine Funktion &lt;code&gt;teile_pizza&lt;/code&gt; zu implementieren, die die Anzahl der Pizzastücke und die Anzahl der Freunde entgegennimmt und die Anzahl der Pizzastücke berechnet, die jeder Freund bekommt. Die Funktion soll die ganzzahlige Anzahl der Pizzastücke pro Person zurückgeben. Wenn es weniger Pizzastücke als Freunde gibt, sollte die Funktion 0 zurückgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>pizzateilung.py</t>
   </si>
   <si>
@@ -214,9 +192,6 @@
   </si>
   <si>
     <t>In der Wochenplanung einer Studentenverbindung wird festgelegt, wer an welchem Tag der Woche für das Abendessen zuständig ist. Die Zuweisung der Kochtage erfolgt zyklisch unter den Mitgliedern. Deine Aufgabe besteht darin, eine Funktion assign_cooking_day zu implementieren, die den Namen des für einen bestimmten Tag zuständigen Mitglieds zurückgibt. Die Funktion nimmt zwei Parameter: day_number, die Nummer des Tages, und members, eine Liste der Namen der Mitglieder. Die Zählung beginnt bei Tag 1, der dem ersten Element in der Mitgliederliste entspricht. Nutze den Modulo-Operator, um den entsprechenden Index in der Mitgliederliste zu bestimmen und den Namen des zuständigen Mitglieds zurückzugeben. Dies ist besonders nützlich, um auch für Tage weit in der Zukunft den Koch zuordnen zu können, ohne die Liste manuell erweitern zu müssen.</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;In der Wochenplanung einer Studentenverbindung wird festgelegt, wer an welchem Tag der Woche für das Abendessen zuständig ist. Die Zuweisung der Kochtage erfolgt zyklisch unter den Mitgliedern. Deine Aufgabe besteht darin, eine Funktion &lt;b&gt;assign_cooking_day&lt;/b&gt; zu implementieren, die den Namen des für einen bestimmten Tag zuständigen Mitglieds zurückgibt. Die Funktion nimmt zwei Parameter: &lt;i&gt;day_number&lt;/i&gt;, die Nummer des Tages, und &lt;i&gt;members&lt;/i&gt;, eine Liste der Namen der Mitglieder. Die Zählung beginnt bei Tag 1, der dem ersten Element in der Mitgliederliste entspricht. Nutze den Modulo-Operator, um den entsprechenden Index in der Mitgliederliste zu bestimmen und den Namen des zuständigen Mitglieds zurückzugeben. Dies ist besonders nützlich, um auch für Tage weit in der Zukunft den Koch zuordnen zu können, ohne die Liste manuell erweitern zu müssen.&lt;/p&gt;</t>
   </si>
   <si>
     <t>cooking_assignment.py</t>
@@ -245,9 +220,6 @@
 # Beispielausführung der Funktion
 if __name__ == "__main__":
     print(assign_cooking_day(10, ["Alice", "Bob", "Charlie", "Dana"]))</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen &lt;code&gt;variable_assignments&lt;/code&gt;, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt.&lt;/p&gt;</t>
   </si>
   <si>
     <t>In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen variable_assignments, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt.</t>
@@ -315,41 +287,7 @@
     unittest.main()</t>
   </si>
   <si>
-    <t>CPP TEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    &lt;h1&gt;CPP Test&lt;/h1&gt;
-</t>
-  </si>
-  <si>
     <t>main.cpp</t>
-  </si>
-  <si>
-    <t>testFile</t>
-  </si>
-  <si>
-    <t>#define DOCTEST_CONFIG_IMPLEMENT_WITH_MAIN
-#include &lt;JsonReporter.h&gt;
-#include "Calculator.h"
-#include "Greeter.h"
-TEST_CASE("Calculator add method") {
-    Calculator calc;
-    SUBCASE("Adding positive numbers") {
-        REQUIRE(calc.add(5, 3) == 8);
-    }
-    SUBCASE("Adding negative numbers") {
-        REQUIRE(calc.add(-2, -4) == -6);
-    }
-}
-TEST_CASE("Greeter greet method") {
-    Greeter greeter;
-    SUBCASE("Greeting a person") {
-        REQUIRE(greeter.greet("John") == "Hello, John!");
-    }
-    SUBCASE("Greeting an empty string") {
-        REQUIRE(greeter.greet("") == "Hello, !");
-    }
-}</t>
   </si>
   <si>
     <t>#include &lt;iostream&gt;
@@ -389,7 +327,34 @@
 };</t>
   </si>
   <si>
-    <t>cpp</t>
+    <t>In dieser Übung geht es darum, die Grundlagen von Variablen in Python zu verstehen und anzuwenden. Deine Aufgabe ist es, eine Funktion namens `initialisiere_variable` zu implementieren, die eine Variable namens `meine_variable` deklariert und mit dem Wert 100 initialisiert. Die Funktion sollte dann diese Variable zurückgeben.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe sollst du die grundlegenden Konzepte der Variablenzuweisung in Python verstehen und anwenden. Erstelle eine Funktion mit dem Namen `variable_assignments`, die zwei Zahlen als Argumente entgegennimmt, diese in zwei Variablen speichert und dann die Summe, Differenz und das Produkt dieser Zahlen berechnet und in einem Tupel zurückgibt.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe sollst du eine Funktion namens `verarbeite_optionale_daten` implementieren, die einen Parameter `daten` entgegennimmt. Dieser Parameter könnte einen beliebigen Wert oder `None` enthalten. Deine Aufgabe ist es, die Funktion so zu gestalten, dass sie überprüft, ob `daten` `None` ist oder nicht. 
+Falls `daten` `None` ist, soll die Funktion den String "Keine Daten vorhanden." zurückgeben. 
+Andernfalls soll die Funktion den String "Daten verarbeitet: [DATEN]" zurückgeben, wobei [DATEN] der Wert des Parameters `daten` ist.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe wirst du eine Funktion namens `convert_to_number` erstellen, die einen String als Eingabeparameter annimmt und versucht, diesen in eine Zahl umzuwandeln. Deine Aufgabe ist es, eine Funktion zu implementieren, die diesen String prüft und in eine ganze Zahl oder eine Fließkommazahl umwandelt, je nachdem, ob der String eine Ganzzahl oder eine Fließkommazahl darstellt.
+Falls der String nicht in eine Zahl umgewandelt werden kann, sollte deine Funktion `None` zurückgeben. Es ist wichtig, Fehlerbehandlung zu implementieren, um sicherzustellen, dass deine Funktion robust und sicher gegenüber ungültigen Eingaben ist.
+Beispiel:
+- Eingabe: "123" -&gt; Ausgabe: 123
+- Eingabe: "45.67" -&gt; Ausgabe: 45.67
+- Eingabe: "abc" -&gt; Ausgabe: None</t>
+  </si>
+  <si>
+    <t>Stell dir vor, du organisierst eine Party mit deinen Freunden und hast mehrere Pizzas bestellt. Um sicherzustellen, dass jeder gleich viele Pizzastücke bekommt, musst du die Gesamtzahl der Pizzastücke durch die Anzahl der Freunde teilen. Deine Aufgabe ist es, eine Funktion `teile_pizza` zu implementieren, die die Anzahl der Pizzastücke und die Anzahl der Freunde entgegennimmt und die Anzahl der Pizzastücke berechnet, die jeder Freund bekommt. Die Funktion soll die ganzzahlige Anzahl der Pizzastücke pro Person zurückgeben. Wenn es weniger Pizzastücke als Freunde gibt, sollte die Funktion 0 zurückgeben.</t>
+  </si>
+  <si>
+    <t>In der Wochenplanung einer Studentenverbindung wird festgelegt, wer an welchem Tag der Woche für das Abendessen zuständig ist. Die Zuweisung der Kochtage erfolgt zyklisch unter den Mitgliedern. 
+Deine Aufgabe besteht darin, eine Funktion **assign_cooking_day** zu implementieren, die den Namen des für einen bestimmten Tag zuständigen Mitglieds zurückgibt. 
+Die Funktion nimmt zwei Parameter:
+- *day_number*, die Nummer des Tages
+- *members*, eine Liste der Namen der Mitglieder
+Die Zählung beginnt bei Tag 1, der dem ersten Element in der Mitgliederliste entspricht. Nutze den Modulo-Operator, um den entsprechenden Index in der Mitgliederliste zu bestimmen und den Namen des zuständigen Mitglieds zurückzugeben. Dies ist besonders nützlich, um auch für Tage weit in der Zukunft den Koch zuordnen zu können, ohne die Liste manuell erweitern zu müssen.</t>
   </si>
 </sst>
 </file>
@@ -892,7 +857,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="28.5"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -953,109 +918,113 @@
       </c>
       <c r="N1" s="13"/>
     </row>
-    <row r="2" spans="1:14" s="6" customFormat="1" ht="409.5">
-      <c r="A2" s="22">
+    <row r="2" spans="1:14" s="25" customFormat="1" ht="150">
+      <c r="A2" s="25">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25">
         <v>1</v>
       </c>
-      <c r="B2" s="23">
+      <c r="C2" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="25">
+        <v>6</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="25">
+        <v>0</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="6" customFormat="1" ht="195">
+      <c r="A3" s="22">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23">
         <v>1</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="24">
-        <v>5</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="24" t="s">
+      <c r="C3" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="24">
+        <v>7</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="24">
+      <c r="I3" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="24">
         <v>0</v>
       </c>
-      <c r="K2" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="25"/>
-    </row>
-    <row r="3" spans="1:14" s="25" customFormat="1" ht="150">
-      <c r="A3" s="25">
-        <v>2</v>
-      </c>
-      <c r="B3" s="25">
-        <v>1</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="25">
-        <v>6</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="25">
-        <v>0</v>
-      </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="6" customFormat="1" ht="195">
+      <c r="L3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" s="6" customFormat="1" ht="225">
       <c r="A4" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="23">
         <v>1</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D4" s="24">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>24</v>
+        <v>57</v>
+      </c>
+      <c r="H4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>27</v>
       </c>
       <c r="J4" s="24">
         <v>0</v>
@@ -1064,40 +1033,40 @@
         <v>16</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="N4" s="25"/>
     </row>
-    <row r="5" spans="1:14" s="6" customFormat="1" ht="225">
+    <row r="5" spans="1:14" s="6" customFormat="1" ht="240">
       <c r="A5" s="22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="23">
         <v>1</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5" s="24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>32</v>
       </c>
       <c r="J5" s="24">
         <v>0</v>
@@ -1105,83 +1074,83 @@
       <c r="K5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="27" t="s">
-        <v>31</v>
+      <c r="L5" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="M5" s="24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N5" s="25"/>
     </row>
-    <row r="6" spans="1:14" s="6" customFormat="1" ht="240">
-      <c r="A6" s="22">
-        <v>5</v>
-      </c>
-      <c r="B6" s="23">
+    <row r="6" spans="1:14" s="6" customFormat="1" ht="165">
+      <c r="A6" s="8">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <v>1</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="24">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="D6" s="8">
+        <v>14</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="24">
+        <v>42</v>
+      </c>
+      <c r="J6" s="8">
         <v>0</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>37</v>
+      <c r="L6" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N6" s="25"/>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1" ht="165">
+    <row r="7" spans="1:14" s="6" customFormat="1" ht="195">
       <c r="A7" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D7" s="8">
         <v>14</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
@@ -1190,54 +1159,12 @@
         <v>16</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N7" s="25"/>
-    </row>
-    <row r="8" spans="1:14" s="6" customFormat="1" ht="195">
-      <c r="A8" s="8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="8">
-        <v>14</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1280,10 +1207,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" customHeight="1">
@@ -1294,10 +1221,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="60" customHeight="1">
@@ -1308,10 +1235,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" customHeight="1">
@@ -1322,10 +1249,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="60" customHeight="1">
@@ -1336,10 +1263,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" customHeight="1">
@@ -1350,10 +1277,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60" customHeight="1">
@@ -1364,10 +1291,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" customHeight="1">
@@ -1378,10 +1305,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="60" customHeight="1">
@@ -1392,10 +1319,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" customHeight="1">
